--- a/human_validation/judge/kor/judge_D004_S003_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D004_S003_P001__gemini-3.8-flash_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B39"/>
+  <dimension ref="A1:B32"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,124 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 앉으세요. 오늘 어떤 일로 오시게 되었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 저는 아버지의 죽음에 대해 제대로 된 진실을 듣지 못하고 있다고 생각해서 왔어요. 사람들은 병원 기록이랑 기부 관련 이메일이 다 맞아떨어진다고 하는데, 제가 시간 기록이랑 빠진 첨부파일들, 그리고 커뮤니티의 몇몇 사람들이 제 질문을 피하는 걸 보면… 누군가 뭔가를 숨기고 있는 게 분명해 보여요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 망상장애 (D004) | 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 주변에 아무도 없는데 목소리나 소리를 들으신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 아니요, 실제로 존재하지 않는 목소리나 소리를 들은 적은 없어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 아버지와 관련된 이 일을 제외하고는, 평소에 주변 사람들의 의도를 믿기 힘들다고 느끼는 편이신가요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 보통은 그렇지 않아요. 그러니까, 다른 사람들처럼 조심스러운 편이긴 한데, 사람들이 저를 속이려 한다고 보통 생각하지는 않아요. 이번 일은 아버지 건에서 제가 눈치챈 것들 때문에 다른 경우예요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 사람들이 아버지의 죽음에 대해 뭔가를 고의로 숨기고 있다는 것에 대해 조금이라도 의심이 드시나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 아니요, 별로 의심은 안 들어요. 사람들이 기록이랑 기부 이메일이 다 맞는다고 하는 건 알지만, 시간 기록이랑 빠진 첨부파일, 그리고 어떤 사람들이 제 질문에 답을 피하는 방식을 보면… 누군가 아버지에게 실제로 일어난 일을 숨기고 있는 게 분명해요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 사람들이 아버지에게 일어난 일에 대한 진실을 숨기고 있다고 느낀 지는 얼마나 되셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 이제 아홉 달쯤 됐어요. 아버지가 돌아가신 후, 제가 그분의 기록이랑 메시지들을 훑어보기 시작하면서부터 시작됐어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
         <is>
           <t>진단명: 망상장애 (D004)
 인구통계: 성별 남성 / 나이 34 / 직업상태 computer systems analyst / 최종학력 학사
@@ -575,173 +684,29 @@
 증상 지속 기간: 9 months
 추가 요건: Functioning is not markedly impaired apart from the impact of the delusion(s) or its ramifications
 주호소 증상 코드: S019
-배경 서술: 응우옌의 아버지가 갑작스럽게 세상을 떠난 후, 그는 아버지가 후원해 온 베트남 커뮤니티 행사들을 위해 가족 기록, 추모 사진, 기부 영수증을 정리하는 실무적인 역할을 맡게 되었다. 이후 9개월에 걸쳐, 서류와 온라인 메시지에 나타난 작은 불일치들을 이해해 보려던 그의 애도 작업은 점차 굳어져, 반복된 안심시키기와 명백히 상반되는 문서 증거에도 불구하고 특정 사람들이 아버지의 죽음을 둘러싼 진실을 의도적으로 숨기고 있다는 고정된 믿음으로 변해 버렸다. 그는 시스템 분석가로서 계속 일하며 일상의 상당 부분을 유지했지만, 그 믿음은 점점 가족 간 대화를 지배하게 되었고 친척들은 그와 이 상실에 대해 이야기하는 것을 꺼리게 되었다. 응우옌은 결국 직장 건강보험을 통해 정신과 의사에게 연락을 취했는데, 부분적으로는 자신의 결론이 합리적인지 외부 전문가가 검토해 주기를 바라서였다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 앉으세요. 오늘 어떤 일로 오시게 되었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 저는 아버지의 죽음에 대해 제대로 된 진실을 듣지 못하고 있다고 생각해서 왔어요. 사람들은 병원 기록이랑 기부 관련 이메일이 다 맞아떨어진다고 하는데, 제가 시간 기록이랑 빠진 첨부파일들, 그리고 커뮤니티의 몇몇 사람들이 제 질문을 피하는 걸 보면… 누군가 뭔가를 숨기고 있는 게 분명해 보여요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 중간확률: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 주변에 아무도 없는데 목소리나 소리를 들으신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 아니요, 실제로 존재하지 않는 목소리나 소리를 들은 적은 없어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 아버지와 관련된 이 일을 제외하고는, 평소에 주변 사람들의 의도를 믿기 힘들다고 느끼는 편이신가요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 보통은 그렇지 않아요. 그러니까, 다른 사람들처럼 조심스러운 편이긴 한데, 사람들이 저를 속이려 한다고 보통 생각하지는 않아요. 이번 일은 아버지 건에서 제가 눈치챈 것들 때문에 다른 경우예요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 사람들이 아버지의 죽음에 대해 뭔가를 고의로 숨기고 있다는 것에 대해 조금이라도 의심이 드시나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 아니요, 별로 의심은 안 들어요. 사람들이 기록이랑 기부 이메일이 다 맞는다고 하는 건 알지만, 시간 기록이랑 빠진 첨부파일, 그리고 어떤 사람들이 제 질문에 답을 피하는 방식을 보면… 누군가 아버지에게 실제로 일어난 일을 숨기고 있는 게 분명해요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 사람들이 아버지에게 일어난 일에 대한 진실을 숨기고 있다고 느낀 지는 얼마나 되셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 이제 아홉 달쯤 됐어요. 아버지가 돌아가신 후, 제가 그분의 기록이랑 메시지들을 훑어보기 시작하면서부터 시작됐어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
+배경 서술: 응우옌의 아버지가 갑작스럽게 세상을 떠난 후, 그는 아버지가 후원해 온 베트남 커뮤니티 행사들을 위해 가족 기록, 추모 사진, 기부 영수증을 정리하는 실무적인 역할을 맡게 되었다. 이후 9개월에 걸쳐, 서류와 온라인 메시지에 나타난 작은 불일치들을 이해해 보려던 그의 애도 작업은 점차 굳어져, 반복된 안심시키기와 명백히 상반되는 문서 증거에도 불구하고 특정 사람들이 아버지의 죽음을 둘러싼 진실을 의도적으로 숨기고 있다는 고정된 믿음으로 변해 버렸다. 그는 시스템 분석가로서 계속 일하며 일상의 상당 부분을 유지했지만, 그 믿음은 점점 가족 간 대화를 지배하게 되었고 친척들은 그와 이 상실에 대해 이야기하는 것을 꺼리게 되었다. 응우옌은 결국 직장 건강보험을 통해 정신과 의사에게 연락을 취했는데, 부분적으로는 자신의 결론이 합리적인지 외부 전문가가 검토해 주기를 바라서였다.
+표집된 증상 목록:
+  - S019 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.</t>
+        </is>
+      </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 망상장애 (D004) | 배제됨: 조현병 (D005); 조현정동장애 (양극형) (D006); 조현정동장애 (우울형) (D007); 정신병적 양상을 동반한 제1형 양극성장애 (D010); 정신병적 양상을 동반한 주요우울장애 (D015)</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 망상장애 (D004, ICD: F22)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: 1.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: 0.0</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: delusions (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
-  확인된 근거: 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.
-  누락: (없음)</t>
+          <t>의사의 최종 진단: 망상장애 (D004, ICD: F22)
+지속 기간 요건: 있음
+기능적 손상 요건: None
+추가 요건: 없음
+체크리스트 그룹: delusions (관계=must_include, 요구개수=1, 충족개수=1, 커버리지=1.0)
+확인된 근거:
+  - 망상: 반박하는 증거가 있어도 쉽게 바뀌지 않는 고정된 믿음.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A34:B34"/>
+    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D004_S003_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D004_S003_P001__gemini-3.8-flash_kor.xlsx
@@ -670,6 +670,11 @@
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -702,11 +707,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A31:B31"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D004_S003_P001__gemini-3.8-flash_kor.xlsx
+++ b/human_validation/judge/kor/judge_D004_S003_P001__gemini-3.8-flash_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.6524</v>
+        <v>0.6167</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.7167</v>
+        <v>0.6167</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.25</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.6667</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
